--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R2" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R3" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2018,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,54 +2128,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R15" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,62 +2235,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2682,7 +2682,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B20" t="n">
         <v>98651</v>
@@ -2712,24 +2712,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R20" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,19 +2781,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B21" t="n">
         <v>98651</v>
@@ -2828,19 +2823,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R21" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3559,6 +3559,715 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129153256</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>575270</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7048889</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129153154</v>
+      </c>
+      <c r="B29" t="n">
+        <v>75155</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>575073</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7048952</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129153115</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>575073</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7048952</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129153347</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>575462</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7048690</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129153291</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575297</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7048889</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129153307</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>575399</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7048757</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129153325</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bodmyråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>575410</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7048748</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Hans Stefan Möller</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R2" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R3" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,66 +887,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133805</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>100817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575360</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048854</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>100812</v>
+        <v>96775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>96770</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B8" t="n">
         <v>79034</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R8" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B9" t="n">
         <v>79034</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R9" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,61 +1548,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,22 +1655,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1678,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1747,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1767,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131738</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,34 +1790,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575393</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048775</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,12 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,50 +1896,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,51 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,45 +2114,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R15" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,57 +2230,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129133688</v>
+        <v>129130593</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575378</v>
+        <v>575163</v>
       </c>
       <c r="R16" t="n">
-        <v>7048841</v>
+        <v>7048972</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3240,45 +3240,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131760</v>
       </c>
       <c r="B25" t="n">
-        <v>92218</v>
+        <v>80139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575384</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7048757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,45 +3454,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131384</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>92223</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575213</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7048950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B4" t="n">
-        <v>100817</v>
+        <v>96778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1006,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B5" t="n">
-        <v>96775</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133805</v>
+        <v>129133384</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>100820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575360</v>
+        <v>575442</v>
       </c>
       <c r="R6" t="n">
-        <v>7048854</v>
+        <v>7048805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1349,7 +1349,7 @@
         <v>129131322</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129131779</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,45 +1560,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131325</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575202</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,22 +1659,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,34 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,12 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,39 +1789,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1858,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,49 +1890,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2018,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2131,7 @@
         <v>129133688</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,51 +2255,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R16" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>129131908</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129131922</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,45 +3240,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131760</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>80139</v>
+        <v>92226</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575384</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7048757</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>92223</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R27" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129153115</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129153307</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129153325</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>96778</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,54 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>96778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133384</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>100820</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575442</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048805</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1671,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1771,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,34 +1794,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,12 +1878,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,51 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,57 +2114,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129133688</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575378</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048841</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,45 +2235,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92226</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,45 +3347,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131760</v>
+        <v>129131384</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>92226</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575384</v>
+        <v>575213</v>
       </c>
       <c r="R26" t="n">
-        <v>7048757</v>
+        <v>7048950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R27" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R2" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R3" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,34 +1789,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1863,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,22 +1883,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,39 +1906,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R13" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2018,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,62 +2128,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R15" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,54 +2244,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R16" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R2" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R3" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1006,45 +1006,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B5" t="n">
-        <v>96778</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>96778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R6" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1560,49 +1560,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,22 +1655,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1678,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1747,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,12 +1767,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1895,45 +1896,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131738</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575393</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048775</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,51 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,57 +2114,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129133688</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575378</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048841</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,45 +2235,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>92226</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,45 +3347,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131384</v>
+        <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>92226</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575213</v>
+        <v>575384</v>
       </c>
       <c r="R26" t="n">
-        <v>7048950</v>
+        <v>7048757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R2" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R3" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,54 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>96788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>96778</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
         <v>129130419</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129131322</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129131779</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,45 +1560,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131325</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575202</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,12 +1659,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1670,7 +1674,7 @@
         <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,39 +1794,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,61 +1878,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2010,7 @@
         <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,62 +2114,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R15" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,57 +2230,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129133688</v>
+        <v>129130593</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575378</v>
+        <v>575163</v>
       </c>
       <c r="R16" t="n">
-        <v>7048841</v>
+        <v>7048972</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>129130470</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,19 +2712,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R20" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,24 +2828,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R21" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2912,7 +2912,7 @@
         <v>129130388</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>129131908</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129131922</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>129153154</v>
       </c>
       <c r="B29" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129153115</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129153307</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129153325</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R2" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R3" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R8" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R9" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,12 +1548,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92233</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,45 +3347,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131760</v>
+        <v>129131384</v>
       </c>
       <c r="B26" t="n">
-        <v>80144</v>
+        <v>92233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575384</v>
+        <v>575213</v>
       </c>
       <c r="R26" t="n">
-        <v>7048757</v>
+        <v>7048950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R27" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,45 +899,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133805</v>
       </c>
       <c r="B4" t="n">
-        <v>100830</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575360</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1018,7 @@
         <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133805</v>
+        <v>129133384</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>100837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575360</v>
+        <v>575442</v>
       </c>
       <c r="R6" t="n">
-        <v>7048854</v>
+        <v>7048805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R8" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R9" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,61 +1548,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131325</v>
+        <v>129131738</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575202</v>
+        <v>575393</v>
       </c>
       <c r="R10" t="n">
-        <v>7048956</v>
+        <v>7048775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1640,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,22 +1767,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,34 +1790,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,62 +1884,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +2007,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,54 +2123,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R15" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,24 +2712,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R20" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2781,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,19 +2823,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R21" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>92240</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>92233</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129133805</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B5" t="n">
-        <v>96795</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B6" t="n">
-        <v>100837</v>
+        <v>96797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R6" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
         <v>129130419</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129131322</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129131779</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>129131738</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,54 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,37 +2125,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,62 +2235,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>129130470</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>129130388</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>129131908</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129131922</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92240</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>92242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,7 +3457,7 @@
         <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>129153154</v>
       </c>
       <c r="B29" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129153115</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129153307</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129153325</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,54 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>96797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R4" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>96797</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92242</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,45 +3454,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131384</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575213</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7048950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>96797</v>
+        <v>100865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>96823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,34 +1683,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1757,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1777,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,39 +1800,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1859,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1869,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,12 +1884,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
         <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>92257</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,45 +3454,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131384</v>
+        <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>92242</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575213</v>
+        <v>575384</v>
       </c>
       <c r="R27" t="n">
-        <v>7048950</v>
+        <v>7048757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>100865</v>
+        <v>100867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,34 +1571,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,22 +1655,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,39 +1678,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,12 +1747,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,34 +1790,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,12 +1884,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
         <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,19 +2712,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R20" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,24 +2828,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R21" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3240,45 +3240,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131760</v>
       </c>
       <c r="B25" t="n">
-        <v>92257</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575384</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7048757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B4" t="n">
-        <v>100867</v>
+        <v>96825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B5" t="n">
-        <v>96824</v>
+        <v>100868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R8" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R9" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,34 +1571,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1645,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,57 +1665,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129131325</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575202</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,12 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,39 +1799,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,61 +1883,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129131738</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575393</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,24 +2712,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R20" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2781,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,19 +2823,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R21" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>92258</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R27" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>96825</v>
+        <v>100872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>100868</v>
+        <v>96829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R8" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R9" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131850</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,39 +1571,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575441</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048704</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,61 +1655,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R11" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1752,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,45 +1784,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133958</v>
+        <v>129131325</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575323</v>
+        <v>575202</v>
       </c>
       <c r="R12" t="n">
-        <v>7048960</v>
+        <v>7048956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,12 +1883,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
         <v>129131738</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2018,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,51 +2139,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R15" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,19 +2712,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R20" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,24 +2828,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R21" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
         <v>129131908</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129131922</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,45 +3240,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131760</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>92261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575384</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7048757</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3350,7 +3350,7 @@
         <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,45 +3454,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131384</v>
+        <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>92258</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575213</v>
+        <v>575384</v>
       </c>
       <c r="R27" t="n">
-        <v>7048950</v>
+        <v>7048757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>129153154</v>
       </c>
       <c r="B29" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129153115</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129153307</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129153325</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -1560,45 +1560,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131325</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575202</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,22 +1659,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,39 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,12 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,49 +1783,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,22 +1878,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131738</v>
+        <v>129131850</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,34 +1901,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575393</v>
+        <v>575441</v>
       </c>
       <c r="R13" t="n">
-        <v>7048775</v>
+        <v>7048704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B4" t="n">
-        <v>100872</v>
+        <v>96831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B5" t="n">
-        <v>96829</v>
+        <v>100874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R8" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R9" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,61 +1548,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,12 +1655,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1674,7 +1670,7 @@
         <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,34 +1790,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,62 +1884,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,51 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>80148</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2139,37 +2125,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,24 +2712,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R20" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2781,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,19 +2823,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R21" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
         <v>129131908</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129131922</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129153115</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129153307</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129153325</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>96831</v>
+        <v>100878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1006,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133384</v>
+        <v>129133805</v>
       </c>
       <c r="B5" t="n">
-        <v>100874</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575442</v>
+        <v>575360</v>
       </c>
       <c r="R5" t="n">
-        <v>7048805</v>
+        <v>7048854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>96835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R6" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R8" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R9" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,34 +1571,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,22 +1660,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,34 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,12 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,12 +1767,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
         <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R27" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R2" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R3" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>100878</v>
+        <v>100886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,54 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>96843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>96835</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,34 +1683,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1757,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,62 +1777,61 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,49 +1900,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,22 +1995,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2018,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,51 +2139,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R15" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,19 +2712,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R20" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,24 +2828,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R21" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
         <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R8" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R9" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,34 +1571,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,22 +1655,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,39 +1678,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,12 +1747,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,49 +1779,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,7 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,45 +1896,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133958</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575323</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048960</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,22 +1995,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,51 +2018,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2139,37 +2125,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92268</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>92268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R8" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R9" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,12 +1548,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1779,50 +1779,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,49 +1890,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +2007,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,54 +2244,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R16" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R2" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R3" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B4" t="n">
-        <v>100886</v>
+        <v>96846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B5" t="n">
-        <v>96843</v>
+        <v>100889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1116,7 @@
         <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R8" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R9" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,22 +1548,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,34 +1571,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1640,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,22 +1660,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,34 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,12 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,61 +1767,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,50 +1896,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,54 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,45 +2235,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,24 +2712,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R20" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2781,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,19 +2823,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R21" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>92268</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1006,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133384</v>
+        <v>129133805</v>
       </c>
       <c r="B5" t="n">
-        <v>100889</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575442</v>
+        <v>575360</v>
       </c>
       <c r="R5" t="n">
-        <v>7048805</v>
+        <v>7048854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>96846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R6" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,7 +1346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129131779</v>
+        <v>129131322</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575384</v>
+        <v>575375</v>
       </c>
       <c r="R8" t="n">
-        <v>7048744</v>
+        <v>7048799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1441,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129131322</v>
+        <v>129131779</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575375</v>
+        <v>575384</v>
       </c>
       <c r="R9" t="n">
-        <v>7048799</v>
+        <v>7048744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,57 +1548,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131738</v>
+        <v>129131325</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575393</v>
+        <v>575202</v>
       </c>
       <c r="R10" t="n">
-        <v>7048775</v>
+        <v>7048956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,12 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131850</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,34 +1682,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575441</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048704</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1756,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1776,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,39 +1799,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,61 +1883,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129131738</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575393</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,37 +2018,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2091,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2101,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,62 +2128,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R15" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,54 +2244,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R16" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -1006,54 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133805</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>96846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575360</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048854</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133487</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>96846</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575437</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048814</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1671,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,39 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1756,12 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131738</v>
+        <v>129131850</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,34 +1901,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575393</v>
+        <v>575441</v>
       </c>
       <c r="R13" t="n">
-        <v>7048775</v>
+        <v>7048704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,62 +2007,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R14" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,57 +2123,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129133688</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575378</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048841</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92271</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,32 +3347,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R2" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R3" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B4" t="n">
-        <v>100889</v>
+        <v>96846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B5" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R5" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1560,49 +1560,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R10" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,57 +1655,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131738</v>
+        <v>129131325</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575393</v>
+        <v>575202</v>
       </c>
       <c r="R11" t="n">
-        <v>7048775</v>
+        <v>7048956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,12 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,34 +1789,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R12" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,7 +1858,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,12 +1878,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2007,54 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,45 +2235,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R25" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,45 +3347,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131384</v>
+        <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>92271</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575213</v>
+        <v>575384</v>
       </c>
       <c r="R26" t="n">
-        <v>7048950</v>
+        <v>7048757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130448</v>
+        <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575072</v>
+        <v>575453</v>
       </c>
       <c r="R2" t="n">
-        <v>7048979</v>
+        <v>7048721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131878</v>
+        <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575453</v>
+        <v>575072</v>
       </c>
       <c r="R3" t="n">
-        <v>7048721</v>
+        <v>7048979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133487</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>96846</v>
+        <v>100889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575437</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048814</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133384</v>
+        <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>100889</v>
+        <v>96846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575442</v>
+        <v>575437</v>
       </c>
       <c r="R5" t="n">
-        <v>7048805</v>
+        <v>7048814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1560,45 +1560,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133958</v>
+        <v>129131325</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575323</v>
+        <v>575202</v>
       </c>
       <c r="R10" t="n">
-        <v>7048960</v>
+        <v>7048956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,61 +1659,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129131325</v>
+        <v>129133958</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575202</v>
+        <v>575323</v>
       </c>
       <c r="R11" t="n">
-        <v>7048956</v>
+        <v>7048960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131738</v>
+        <v>129131850</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,34 +1789,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575393</v>
+        <v>575441</v>
       </c>
       <c r="R12" t="n">
-        <v>7048775</v>
+        <v>7048704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,12 +1863,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,39 +1906,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R13" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +2007,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129131175</v>
+        <v>129133688</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575281</v>
+        <v>575378</v>
       </c>
       <c r="R14" t="n">
-        <v>7048945</v>
+        <v>7048841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129130593</v>
+        <v>129131175</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,51 +2134,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575163</v>
+        <v>575281</v>
       </c>
       <c r="R15" t="n">
-        <v>7048972</v>
+        <v>7048945</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2208,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,57 +2230,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129133688</v>
+        <v>129130593</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575378</v>
+        <v>575163</v>
       </c>
       <c r="R16" t="n">
-        <v>7048841</v>
+        <v>7048972</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R26" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R27" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -899,45 +899,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133384</v>
+        <v>129133805</v>
       </c>
       <c r="B4" t="n">
-        <v>100889</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575442</v>
+        <v>575360</v>
       </c>
       <c r="R4" t="n">
-        <v>7048805</v>
+        <v>7048854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,54 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133805</v>
+        <v>129133384</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>100889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575360</v>
+        <v>575442</v>
       </c>
       <c r="R6" t="n">
-        <v>7048854</v>
+        <v>7048805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1560,49 +1560,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R10" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1645,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131850</v>
+        <v>129131738</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,39 +1795,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575441</v>
+        <v>575393</v>
       </c>
       <c r="R12" t="n">
-        <v>7048704</v>
+        <v>7048775</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1853,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1863,12 +1864,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,45 +1896,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131738</v>
+        <v>129131325</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575393</v>
+        <v>575202</v>
       </c>
       <c r="R13" t="n">
-        <v>7048775</v>
+        <v>7048956</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,54 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133688</v>
+        <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575378</v>
+        <v>575281</v>
       </c>
       <c r="R14" t="n">
-        <v>7048841</v>
+        <v>7048945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129131175</v>
+        <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,37 +2125,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575281</v>
+        <v>575163</v>
       </c>
       <c r="R15" t="n">
-        <v>7048945</v>
+        <v>7048972</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,7 +2198,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2208,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,62 +2235,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129130593</v>
+        <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575163</v>
+        <v>575378</v>
       </c>
       <c r="R16" t="n">
-        <v>7048972</v>
+        <v>7048841</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2682,7 +2682,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B20" t="n">
         <v>98727</v>
@@ -2712,19 +2712,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R20" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,19 +2786,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B21" t="n">
         <v>98727</v>
@@ -2823,24 +2828,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R21" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129131154</v>
+        <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,34 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575199</v>
+        <v>575384</v>
       </c>
       <c r="R26" t="n">
-        <v>7049020</v>
+        <v>7048757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131760</v>
+        <v>129131154</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,34 +3465,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575384</v>
+        <v>575199</v>
       </c>
       <c r="R27" t="n">
-        <v>7048757</v>
+        <v>7049020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48181-2025 artfynd.xlsx
+++ b/artfynd/A 48181-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129131878</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129130448</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,54 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133805</v>
+        <v>129133384</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>100918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575360</v>
+        <v>575442</v>
       </c>
       <c r="R4" t="n">
-        <v>7048854</v>
+        <v>7048805</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1009,7 @@
         <v>129133487</v>
       </c>
       <c r="B5" t="n">
-        <v>96846</v>
+        <v>96875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,45 +1113,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129133384</v>
+        <v>129133805</v>
       </c>
       <c r="B6" t="n">
-        <v>100889</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575442</v>
+        <v>575360</v>
       </c>
       <c r="R6" t="n">
-        <v>7048805</v>
+        <v>7048854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
         <v>129130419</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>129131322</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>129131779</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,50 +1560,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129131850</v>
+        <v>129131325</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575441</v>
+        <v>575202</v>
       </c>
       <c r="R10" t="n">
-        <v>7048704</v>
+        <v>7048956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,12 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129133958</v>
+        <v>129131738</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,34 +1682,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575323</v>
+        <v>575393</v>
       </c>
       <c r="R11" t="n">
-        <v>7048960</v>
+        <v>7048775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,7 +1741,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1751,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,22 +1771,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129131738</v>
+        <v>129133958</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,34 +1794,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575393</v>
+        <v>575323</v>
       </c>
       <c r="R12" t="n">
-        <v>7048775</v>
+        <v>7048960</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,61 +1878,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129131325</v>
+        <v>129131850</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575202</v>
+        <v>575441</v>
       </c>
       <c r="R13" t="n">
-        <v>7048956</v>
+        <v>7048704</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2010,7 @@
         <v>129131175</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>129130593</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129133688</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>129131696</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129131805</v>
       </c>
       <c r="B18" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>129130470</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129131377</v>
+        <v>129131283</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,24 +2712,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodmyråsen, Bodmyråsen, Ång</t>
+          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575420</v>
+        <v>575237</v>
       </c>
       <c r="R20" t="n">
-        <v>7048776</v>
+        <v>7048982</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2771,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,22 +2781,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129131283</v>
+        <v>129131377</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,19 +2823,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Måns-Karlsbäcken, Måns-Karlsbäcken, Ång</t>
+          <t>Bodmyråsen, Bodmyråsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575237</v>
+        <v>575420</v>
       </c>
       <c r="R21" t="n">
-        <v>7048982</v>
+        <v>7048776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,12 +2897,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2912,7 +2912,7 @@
         <v>129130388</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>129131908</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>129131922</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,32 +3240,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129131384</v>
+        <v>129131154</v>
       </c>
       <c r="B25" t="n">
-        <v>92271</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575213</v>
+        <v>575199</v>
       </c>
       <c r="R25" t="n">
-        <v>7048950</v>
+        <v>7049020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3350,7 +3350,7 @@
         <v>129131760</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3454,32 +3454,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129131154</v>
+        <v>129131384</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>92299</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575199</v>
+        <v>575213</v>
       </c>
       <c r="R27" t="n">
-        <v>7049020</v>
+        <v>7048950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
         <v>129153256</v>
       </c>
       <c r="B28" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>129153154</v>
       </c>
       <c r="B29" t="n">
-        <v>75161</v>
+        <v>75182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>129153115</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>129153347</v>
       </c>
       <c r="B31" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>129153291</v>
       </c>
       <c r="B32" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>129153307</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>129153325</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
